--- a/3rd_SEMESTER/Statistics/Multiple-Regression/multipleregression.xlsx
+++ b/3rd_SEMESTER/Statistics/Multiple-Regression/multipleregression.xlsx
@@ -1,47 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gaurav Gautam\Desktop\BSc.CSIT\3rd_SEMESTER\Statistics\Multiple-Regression\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{320CDE6B-36B2-4192-A163-762993450789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{DDA68869-E468-4D0F-AC27-792509C16D96}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -96,39 +79,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -161,26 +144,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -213,23 +179,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -291,6 +240,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -299,13 +255,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -370,40 +319,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65999E30-6E07-40BD-940F-CABC82D9142F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/3rd_SEMESTER/Statistics/Multiple-Regression/multipleregression.xlsx
+++ b/3rd_SEMESTER/Statistics/Multiple-Regression/multipleregression.xlsx
@@ -1,27 +1,142 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dines\Documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986DDE7D-6264-4CB1-9D08-6B12CA84CFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{04D2B7D5-520C-411C-9FD4-41BD9A962C99}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
+  <si>
+    <t>Hours Stuided</t>
+  </si>
+  <si>
+    <t>Attendence</t>
+  </si>
+  <si>
+    <t>Sleep_hours</t>
+  </si>
+  <si>
+    <t>ExamScore</t>
+  </si>
+  <si>
+    <t>SUMMARY OUTPUT</t>
+  </si>
+  <si>
+    <t>Regression Statistics</t>
+  </si>
+  <si>
+    <t>Multiple R</t>
+  </si>
+  <si>
+    <t>R Square</t>
+  </si>
+  <si>
+    <t>Adjusted R Square</t>
+  </si>
+  <si>
+    <t>Standard Error</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>t Stat</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>Lower 95%</t>
+  </si>
+  <si>
+    <t>Upper 95%</t>
+  </si>
+  <si>
+    <t>Lower 95.0%</t>
+  </si>
+  <si>
+    <t>Upper 95.0%</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -37,7 +152,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -45,12 +160,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -69,9 +212,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -85,7 +228,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -97,7 +240,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -109,7 +252,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -144,6 +287,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -179,9 +339,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -323,17 +500,746 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25BE2767-9AC5-48FD-B747-F6F40CA8D2E7}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.99683457153067823</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.99367916299875092</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.99130884912328243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.99921413019880989</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1255.679235642755</v>
+      </c>
+      <c r="D12" s="1">
+        <v>418.55974521425168</v>
+      </c>
+      <c r="E12" s="1">
+        <v>419.21838845177922</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3.9183034146810396E-9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <v>7.9874310239117134</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.99842887798896418</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1263.6666666666667</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1">
+        <v>5.7041692213365902</v>
+      </c>
+      <c r="C17" s="1">
+        <v>11.931758774899549</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.47806608639593556</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.6453935856795151</v>
+      </c>
+      <c r="F17" s="1">
+        <v>-21.810515853840378</v>
+      </c>
+      <c r="G17" s="1">
+        <v>33.218854296513555</v>
+      </c>
+      <c r="H17" s="1">
+        <v>-21.810515853840378</v>
+      </c>
+      <c r="I17" s="1">
+        <v>33.218854296513555</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3.4150827713059475</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1.0470788306266317</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3.2615335841162669</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1.1500877894178368E-2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1.0005146579961912</v>
+      </c>
+      <c r="G18" s="1">
+        <v>5.8296508846157042</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1.0005146579961912</v>
+      </c>
+      <c r="I18" s="1">
+        <v>5.8296508846157042</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.36358062538320057</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.17141633489035149</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2.1210383807107371</v>
+      </c>
+      <c r="E19" s="1">
+        <v>6.6717275098101089E-2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>-3.1706151715492292E-2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.75886740248189344</v>
+      </c>
+      <c r="H19" s="1">
+        <v>-3.1706151715492292E-2</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.75886740248189344</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1.2896995708154513</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1.1118687268128582</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1.1599387047357115</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.27951830024649038</v>
+      </c>
+      <c r="F20" s="2">
+        <v>-1.2742743110191921</v>
+      </c>
+      <c r="G20" s="2">
+        <v>3.8536734526500949</v>
+      </c>
+      <c r="H20" s="2">
+        <v>-1.2742743110191921</v>
+      </c>
+      <c r="I20" s="2">
+        <v>3.8536734526500949</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFAFB5A6-AB3C-46D6-8D5D-60AA0A4C4168}">
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>65</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>65</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>90</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>72</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.99683457153067823</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>92</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>78</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.99367916299875092</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>68</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.99130884912328243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>72</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>54</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.99921413019880989</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>88</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>67</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>91</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>82</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>62</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1255.679235642755</v>
+      </c>
+      <c r="I15" s="1">
+        <v>418.55974521425168</v>
+      </c>
+      <c r="J15" s="1">
+        <v>419.21838845177922</v>
+      </c>
+      <c r="K15" s="1">
+        <v>3.9183034146810396E-9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>7.9874310239117134</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.99842887798896418</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="6:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="2">
+        <v>11</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1263.6666666666667</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="6:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="F20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="1">
+        <v>5.7041692213365902</v>
+      </c>
+      <c r="H20" s="1">
+        <v>11.931758774899549</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.47806608639593556</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.6453935856795151</v>
+      </c>
+      <c r="K20" s="1">
+        <v>-21.810515853840378</v>
+      </c>
+      <c r="L20" s="1">
+        <v>33.218854296513555</v>
+      </c>
+      <c r="M20" s="1">
+        <v>-21.810515853840378</v>
+      </c>
+      <c r="N20" s="1">
+        <v>33.218854296513555</v>
+      </c>
+    </row>
+    <row r="21" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="F21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>3.4150827713059475</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1.0470788306266317</v>
+      </c>
+      <c r="I21" s="1">
+        <v>3.2615335841162669</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1.1500877894178368E-2</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1.0005146579961912</v>
+      </c>
+      <c r="L21" s="1">
+        <v>5.8296508846157042</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1.0005146579961912</v>
+      </c>
+      <c r="N21" s="1">
+        <v>5.8296508846157042</v>
+      </c>
+    </row>
+    <row r="22" spans="6:14" x14ac:dyDescent="0.3">
+      <c r="F22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.36358062538320057</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.17141633489035149</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2.1210383807107371</v>
+      </c>
+      <c r="J22" s="1">
+        <v>6.6717275098101089E-2</v>
+      </c>
+      <c r="K22" s="1">
+        <v>-3.1706151715492292E-2</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0.75886740248189344</v>
+      </c>
+      <c r="M22" s="1">
+        <v>-3.1706151715492292E-2</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0.75886740248189344</v>
+      </c>
+    </row>
+    <row r="23" spans="6:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1.2896995708154513</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1.1118687268128582</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1.1599387047357115</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0.27951830024649038</v>
+      </c>
+      <c r="K23" s="2">
+        <v>-1.2742743110191921</v>
+      </c>
+      <c r="L23" s="2">
+        <v>3.8536734526500949</v>
+      </c>
+      <c r="M23" s="2">
+        <v>-1.2742743110191921</v>
+      </c>
+      <c r="N23" s="2">
+        <v>3.8536734526500949</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>